--- a/doc/werds.xlsx
+++ b/doc/werds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skaly\Build\werdnerd_web\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e557a299db13c36/Desktop/PoisonIvy2.0/Build/werdnerd_web/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5607ED0A-BF8B-4D8B-A091-BD012910ED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5607ED0A-BF8B-4D8B-A091-BD012910ED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA710E6-B3A0-4A2B-A81A-DADB00B1EED2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="werds" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6307" uniqueCount="1423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6307" uniqueCount="1425">
   <si>
     <t>werd</t>
   </si>
@@ -4310,6 +4310,12 @@
   </si>
   <si>
     <t>A cowardly despicable person</t>
+  </si>
+  <si>
+    <t>que sera sera</t>
+  </si>
+  <si>
+    <t>omnia causa fliunt</t>
   </si>
 </sst>
 </file>
@@ -5400,23 +5406,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB077F1C-3FA9-460B-A3E5-73EBB10064DD}">
   <dimension ref="A1:S339"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="3" max="3" width="4.6328125" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" customWidth="1"/>
+    <col min="5" max="6" width="6.36328125" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10.77734375" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" customWidth="1"/>
-    <col min="13" max="13" width="5.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" customWidth="1"/>
+    <col min="11" max="11" width="12.08984375" customWidth="1"/>
+    <col min="12" max="12" width="9.54296875" customWidth="1"/>
+    <col min="13" max="13" width="5.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5457,7 +5463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>780</v>
       </c>
@@ -5490,7 +5496,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -5525,7 +5531,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -5560,7 +5566,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>447</v>
       </c>
@@ -5592,7 +5598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -5624,7 +5630,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -5656,7 +5662,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>870</v>
       </c>
@@ -5686,7 +5692,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>781</v>
       </c>
@@ -5716,7 +5722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>38</v>
       </c>
@@ -5746,7 +5752,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -5778,7 +5784,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>48</v>
       </c>
@@ -5810,7 +5816,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>50</v>
       </c>
@@ -5842,7 +5848,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>721</v>
       </c>
@@ -5874,7 +5880,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
@@ -5906,7 +5912,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>56</v>
       </c>
@@ -5938,7 +5944,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>722</v>
       </c>
@@ -5970,7 +5976,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>61</v>
       </c>
@@ -6002,7 +6008,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
@@ -6034,7 +6040,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>68</v>
       </c>
@@ -6066,7 +6072,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>70</v>
       </c>
@@ -6098,7 +6104,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>72</v>
       </c>
@@ -6130,7 +6136,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>723</v>
       </c>
@@ -6160,7 +6166,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>871</v>
       </c>
@@ -6192,7 +6198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>74</v>
       </c>
@@ -6224,7 +6230,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>724</v>
       </c>
@@ -6256,7 +6262,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>872</v>
       </c>
@@ -6288,7 +6294,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>77</v>
       </c>
@@ -6318,7 +6324,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>82</v>
       </c>
@@ -6350,7 +6356,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>84</v>
       </c>
@@ -6382,7 +6388,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>725</v>
       </c>
@@ -6414,7 +6420,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>726</v>
       </c>
@@ -6446,7 +6452,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>86</v>
       </c>
@@ -6478,7 +6484,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>873</v>
       </c>
@@ -6510,7 +6516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>88</v>
       </c>
@@ -6542,7 +6548,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>874</v>
       </c>
@@ -6576,7 +6582,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>93</v>
       </c>
@@ -6608,7 +6614,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>1161</v>
       </c>
@@ -6640,7 +6646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>875</v>
       </c>
@@ -6672,7 +6678,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>876</v>
       </c>
@@ -6704,7 +6710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>803</v>
       </c>
@@ -6736,7 +6742,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>804</v>
       </c>
@@ -6768,7 +6774,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>805</v>
       </c>
@@ -6800,7 +6806,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>691</v>
       </c>
@@ -6832,7 +6838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>806</v>
       </c>
@@ -6864,7 +6870,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>99</v>
       </c>
@@ -6894,7 +6900,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>877</v>
       </c>
@@ -6926,7 +6932,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>878</v>
       </c>
@@ -6956,7 +6962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>101</v>
       </c>
@@ -6988,7 +6994,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>807</v>
       </c>
@@ -7020,7 +7026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>727</v>
       </c>
@@ -7054,7 +7060,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>104</v>
       </c>
@@ -7086,7 +7092,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>808</v>
       </c>
@@ -7116,7 +7122,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>108</v>
       </c>
@@ -7148,7 +7154,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>110</v>
       </c>
@@ -7180,7 +7186,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>809</v>
       </c>
@@ -7212,7 +7218,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>810</v>
       </c>
@@ -7242,7 +7248,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>112</v>
       </c>
@@ -7274,7 +7280,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>879</v>
       </c>
@@ -7308,7 +7314,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>115</v>
       </c>
@@ -7340,7 +7346,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>880</v>
       </c>
@@ -7370,7 +7376,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>811</v>
       </c>
@@ -7400,7 +7406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>117</v>
       </c>
@@ -7432,7 +7438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
         <v>812</v>
       </c>
@@ -7464,7 +7470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>881</v>
       </c>
@@ -7494,7 +7500,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>882</v>
       </c>
@@ -7528,7 +7534,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>120</v>
       </c>
@@ -7560,7 +7566,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>813</v>
       </c>
@@ -7592,7 +7598,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>124</v>
       </c>
@@ -7624,7 +7630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>883</v>
       </c>
@@ -7654,7 +7660,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>719</v>
       </c>
@@ -7684,7 +7690,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>127</v>
       </c>
@@ -7714,7 +7720,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>129</v>
       </c>
@@ -7746,7 +7752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>884</v>
       </c>
@@ -7776,7 +7782,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>885</v>
       </c>
@@ -7806,7 +7812,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
         <v>814</v>
       </c>
@@ -7836,7 +7842,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>815</v>
       </c>
@@ -7866,7 +7872,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>131</v>
       </c>
@@ -7898,7 +7904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>886</v>
       </c>
@@ -7928,7 +7934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>134</v>
       </c>
@@ -7960,7 +7966,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>816</v>
       </c>
@@ -7990,7 +7996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>887</v>
       </c>
@@ -8020,7 +8026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>817</v>
       </c>
@@ -8050,7 +8056,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>888</v>
       </c>
@@ -8080,7 +8086,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>889</v>
       </c>
@@ -8114,7 +8120,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>890</v>
       </c>
@@ -8144,7 +8150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>137</v>
       </c>
@@ -8176,7 +8182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>891</v>
       </c>
@@ -8206,7 +8212,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>892</v>
       </c>
@@ -8236,7 +8242,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>893</v>
       </c>
@@ -8266,7 +8272,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>894</v>
       </c>
@@ -8296,7 +8302,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>895</v>
       </c>
@@ -8326,7 +8332,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>896</v>
       </c>
@@ -8356,7 +8362,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>897</v>
       </c>
@@ -8386,7 +8392,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>898</v>
       </c>
@@ -8416,7 +8422,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>899</v>
       </c>
@@ -8446,7 +8452,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>900</v>
       </c>
@@ -8476,7 +8482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>901</v>
       </c>
@@ -8506,7 +8512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
         <v>818</v>
       </c>
@@ -8536,7 +8542,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>902</v>
       </c>
@@ -8566,7 +8572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
         <v>819</v>
       </c>
@@ -8596,7 +8602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>903</v>
       </c>
@@ -8626,7 +8632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>904</v>
       </c>
@@ -8656,7 +8662,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>905</v>
       </c>
@@ -8690,7 +8696,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>906</v>
       </c>
@@ -8720,7 +8726,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="8" t="s">
         <v>820</v>
       </c>
@@ -8750,7 +8756,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>139</v>
       </c>
@@ -8782,7 +8788,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
         <v>821</v>
       </c>
@@ -8815,7 +8821,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="8" t="s">
         <v>822</v>
       </c>
@@ -8848,7 +8854,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="8" t="s">
         <v>823</v>
       </c>
@@ -8881,7 +8887,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>907</v>
       </c>
@@ -8914,7 +8920,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="8" t="s">
         <v>824</v>
       </c>
@@ -8947,7 +8953,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>141</v>
       </c>
@@ -8982,7 +8988,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>908</v>
       </c>
@@ -9015,7 +9021,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>144</v>
       </c>
@@ -9050,7 +9056,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>147</v>
       </c>
@@ -9085,7 +9091,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>909</v>
       </c>
@@ -9118,7 +9124,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>910</v>
       </c>
@@ -9151,7 +9157,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>150</v>
       </c>
@@ -9186,7 +9192,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>825</v>
       </c>
@@ -9217,7 +9223,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>911</v>
       </c>
@@ -9250,7 +9256,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>152</v>
       </c>
@@ -9285,7 +9291,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>154</v>
       </c>
@@ -9320,7 +9326,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>912</v>
       </c>
@@ -9353,7 +9359,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>913</v>
       </c>
@@ -9390,7 +9396,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>914</v>
       </c>
@@ -9423,7 +9429,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="127" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>156</v>
       </c>
@@ -9458,7 +9464,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>915</v>
       </c>
@@ -9491,7 +9497,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>916</v>
       </c>
@@ -9519,7 +9525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="8" t="s">
         <v>826</v>
       </c>
@@ -9549,7 +9555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>917</v>
       </c>
@@ -9579,7 +9585,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>918</v>
       </c>
@@ -9609,7 +9615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>919</v>
       </c>
@@ -9639,7 +9645,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
         <v>920</v>
       </c>
@@ -9673,7 +9679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>159</v>
       </c>
@@ -9705,7 +9711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>162</v>
       </c>
@@ -9737,7 +9743,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>921</v>
       </c>
@@ -9771,7 +9777,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>922</v>
       </c>
@@ -9801,7 +9807,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>827</v>
       </c>
@@ -9831,7 +9837,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>923</v>
       </c>
@@ -9861,7 +9867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>924</v>
       </c>
@@ -9891,7 +9897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>925</v>
       </c>
@@ -9921,7 +9927,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>926</v>
       </c>
@@ -9951,7 +9957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>927</v>
       </c>
@@ -9981,7 +9987,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>697</v>
       </c>
@@ -10013,7 +10019,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>167</v>
       </c>
@@ -10045,7 +10051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>928</v>
       </c>
@@ -10075,7 +10081,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>929</v>
       </c>
@@ -10105,7 +10111,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>828</v>
       </c>
@@ -10135,7 +10141,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>930</v>
       </c>
@@ -10169,7 +10175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="8" t="s">
         <v>829</v>
       </c>
@@ -10197,7 +10203,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>931</v>
       </c>
@@ -10227,7 +10233,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>932</v>
       </c>
@@ -10257,7 +10263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>933</v>
       </c>
@@ -10287,7 +10293,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="8" t="s">
         <v>830</v>
       </c>
@@ -10317,7 +10323,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>934</v>
       </c>
@@ -10347,7 +10353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="8" t="s">
         <v>831</v>
       </c>
@@ -10377,7 +10383,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>935</v>
       </c>
@@ -10407,7 +10413,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="8" t="s">
         <v>832</v>
       </c>
@@ -10437,7 +10443,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
         <v>172</v>
       </c>
@@ -10469,7 +10475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="8" t="s">
         <v>936</v>
       </c>
@@ -10499,7 +10505,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>833</v>
       </c>
@@ -10533,7 +10539,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>175</v>
       </c>
@@ -10565,7 +10571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>834</v>
       </c>
@@ -10599,7 +10605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
         <v>937</v>
       </c>
@@ -10629,7 +10635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
         <v>835</v>
       </c>
@@ -10659,7 +10665,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>177</v>
       </c>
@@ -10691,7 +10697,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
         <v>836</v>
       </c>
@@ -10721,7 +10727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="9" t="s">
         <v>837</v>
       </c>
@@ -10751,7 +10757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="8" t="s">
         <v>838</v>
       </c>
@@ -10781,7 +10787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>180</v>
       </c>
@@ -10813,7 +10819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="8" t="s">
         <v>839</v>
       </c>
@@ -10843,7 +10849,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="8" t="s">
         <v>840</v>
       </c>
@@ -10873,7 +10879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
         <v>182</v>
       </c>
@@ -10905,7 +10911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>184</v>
       </c>
@@ -10935,7 +10941,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
         <v>188</v>
       </c>
@@ -10967,7 +10973,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
         <v>938</v>
       </c>
@@ -10997,7 +11003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="8" t="s">
         <v>841</v>
       </c>
@@ -11027,7 +11033,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="9" t="s">
         <v>779</v>
       </c>
@@ -11059,7 +11065,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
         <v>190</v>
       </c>
@@ -11091,7 +11097,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>939</v>
       </c>
@@ -11125,7 +11131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
         <v>842</v>
       </c>
@@ -11159,7 +11165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>193</v>
       </c>
@@ -11191,7 +11197,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
         <v>195</v>
       </c>
@@ -11223,7 +11229,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
         <v>940</v>
       </c>
@@ -11253,7 +11259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
         <v>843</v>
       </c>
@@ -11287,7 +11293,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="9" t="s">
         <v>941</v>
       </c>
@@ -11317,7 +11323,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="8" t="s">
         <v>844</v>
       </c>
@@ -11347,7 +11353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>198</v>
       </c>
@@ -11379,7 +11385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="8" t="s">
         <v>845</v>
       </c>
@@ -11409,7 +11415,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>202</v>
       </c>
@@ -11441,7 +11447,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="8" t="s">
         <v>846</v>
       </c>
@@ -11469,7 +11475,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>204</v>
       </c>
@@ -11501,7 +11507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="8" t="s">
         <v>847</v>
       </c>
@@ -11531,7 +11537,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>206</v>
       </c>
@@ -11563,7 +11569,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
         <v>208</v>
       </c>
@@ -11595,7 +11601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>212</v>
       </c>
@@ -11627,7 +11633,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="8" t="s">
         <v>848</v>
       </c>
@@ -11657,7 +11663,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>214</v>
       </c>
@@ -11689,7 +11695,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>217</v>
       </c>
@@ -11719,7 +11725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
         <v>219</v>
       </c>
@@ -11751,7 +11757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="8" t="s">
         <v>849</v>
       </c>
@@ -11783,7 +11789,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
         <v>221</v>
       </c>
@@ -11815,7 +11821,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>224</v>
       </c>
@@ -11847,7 +11853,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="8" t="s">
         <v>850</v>
       </c>
@@ -11877,7 +11883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>227</v>
       </c>
@@ -11909,7 +11915,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
         <v>942</v>
       </c>
@@ -11939,7 +11945,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="8" t="s">
         <v>851</v>
       </c>
@@ -11969,7 +11975,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="8" t="s">
         <v>852</v>
       </c>
@@ -11999,7 +12005,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="8" t="s">
         <v>853</v>
       </c>
@@ -12027,7 +12033,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
         <v>231</v>
       </c>
@@ -12059,7 +12065,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>442</v>
       </c>
@@ -12093,7 +12099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
         <v>234</v>
       </c>
@@ -12125,7 +12131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="8" t="s">
         <v>943</v>
       </c>
@@ -12155,7 +12161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
         <v>237</v>
       </c>
@@ -12185,7 +12191,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="8" t="s">
         <v>854</v>
       </c>
@@ -12215,7 +12221,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
         <v>784</v>
       </c>
@@ -12247,7 +12253,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>240</v>
       </c>
@@ -12279,7 +12285,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
         <v>944</v>
       </c>
@@ -12309,7 +12315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" s="8" t="s">
         <v>855</v>
       </c>
@@ -12339,7 +12345,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
         <v>243</v>
       </c>
@@ -12371,7 +12377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="8" t="s">
         <v>856</v>
       </c>
@@ -12399,7 +12405,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="8" t="s">
         <v>857</v>
       </c>
@@ -12429,7 +12435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>245</v>
       </c>
@@ -12459,7 +12465,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
         <v>246</v>
       </c>
@@ -12491,7 +12497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>249</v>
       </c>
@@ -12523,7 +12529,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
         <v>945</v>
       </c>
@@ -12557,7 +12563,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>252</v>
       </c>
@@ -12587,7 +12593,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
         <v>256</v>
       </c>
@@ -12619,7 +12625,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>698</v>
       </c>
@@ -12651,7 +12657,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="7" t="s">
         <v>858</v>
       </c>
@@ -12685,7 +12691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>260</v>
       </c>
@@ -12717,7 +12723,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
         <v>263</v>
       </c>
@@ -12749,7 +12755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>265</v>
       </c>
@@ -12781,7 +12787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="8" t="s">
         <v>859</v>
       </c>
@@ -12811,7 +12817,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" s="7" t="s">
         <v>946</v>
       </c>
@@ -12841,7 +12847,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
         <v>267</v>
       </c>
@@ -12873,7 +12879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="7" t="s">
         <v>947</v>
       </c>
@@ -12903,7 +12909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="7" t="s">
         <v>948</v>
       </c>
@@ -12937,7 +12943,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>717</v>
       </c>
@@ -12967,7 +12973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
         <v>949</v>
       </c>
@@ -12997,7 +13003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="7" t="s">
         <v>950</v>
       </c>
@@ -13027,7 +13033,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" s="3" t="s">
         <v>951</v>
       </c>
@@ -13057,7 +13063,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
         <v>952</v>
       </c>
@@ -13087,7 +13093,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
         <v>272</v>
       </c>
@@ -13119,7 +13125,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>274</v>
       </c>
@@ -13151,7 +13157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
         <v>278</v>
       </c>
@@ -13183,7 +13189,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>283</v>
       </c>
@@ -13215,7 +13221,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A249" s="7" t="s">
         <v>953</v>
       </c>
@@ -13245,7 +13251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A250" s="8" t="s">
         <v>860</v>
       </c>
@@ -13275,7 +13281,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
         <v>286</v>
       </c>
@@ -13307,7 +13313,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>289</v>
       </c>
@@ -13337,7 +13343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="8" t="s">
         <v>861</v>
       </c>
@@ -13367,7 +13373,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" s="7" t="s">
         <v>954</v>
       </c>
@@ -13401,7 +13407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" s="8" t="s">
         <v>862</v>
       </c>
@@ -13431,7 +13437,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" s="7" t="s">
         <v>863</v>
       </c>
@@ -13461,7 +13467,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
         <v>294</v>
       </c>
@@ -13491,7 +13497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>297</v>
       </c>
@@ -13523,7 +13529,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
         <v>300</v>
       </c>
@@ -13555,7 +13561,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="8" t="s">
         <v>864</v>
       </c>
@@ -13583,7 +13589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
         <v>302</v>
       </c>
@@ -13615,7 +13621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>304</v>
       </c>
@@ -13647,7 +13653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" s="7" t="s">
         <v>955</v>
       </c>
@@ -13677,7 +13683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A264" s="7" t="s">
         <v>865</v>
       </c>
@@ -13707,7 +13713,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A265" s="8" t="s">
         <v>866</v>
       </c>
@@ -13737,9 +13743,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
-        <v>956</v>
+        <v>1424</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>307</v>
@@ -13767,7 +13773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
         <v>309</v>
       </c>
@@ -13799,7 +13805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A268" s="8" t="s">
         <v>867</v>
       </c>
@@ -13829,7 +13835,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
         <v>311</v>
       </c>
@@ -13861,7 +13867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A270" s="8" t="s">
         <v>868</v>
       </c>
@@ -13891,7 +13897,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A271" s="8" t="s">
         <v>785</v>
       </c>
@@ -13919,7 +13925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A272" s="7" t="s">
         <v>957</v>
       </c>
@@ -13949,7 +13955,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A273" s="7" t="s">
         <v>958</v>
       </c>
@@ -13979,7 +13985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A274" s="8" t="s">
         <v>869</v>
       </c>
@@ -14009,7 +14015,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
         <v>314</v>
       </c>
@@ -14041,7 +14047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A276" s="7" t="s">
         <v>959</v>
       </c>
@@ -14071,7 +14077,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A277" s="7" t="s">
         <v>960</v>
       </c>
@@ -14101,7 +14107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>316</v>
       </c>
@@ -14133,7 +14139,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A279" s="7" t="s">
         <v>961</v>
       </c>
@@ -14167,7 +14173,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>318</v>
       </c>
@@ -14199,7 +14205,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
         <v>320</v>
       </c>
@@ -14231,7 +14237,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
         <v>323</v>
       </c>
@@ -14263,7 +14269,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
         <v>325</v>
       </c>
@@ -14295,7 +14301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A284" s="7" t="s">
         <v>963</v>
       </c>
@@ -14329,9 +14335,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
-        <v>962</v>
+        <v>1423</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>327</v>
@@ -14359,7 +14365,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
         <v>329</v>
       </c>
@@ -14391,7 +14397,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
         <v>333</v>
       </c>
@@ -14423,7 +14429,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A288" s="7" t="s">
         <v>964</v>
       </c>
@@ -14453,7 +14459,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
         <v>335</v>
       </c>
@@ -14485,7 +14491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>337</v>
       </c>
@@ -14517,7 +14523,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
         <v>340</v>
       </c>
@@ -14549,7 +14555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>342</v>
       </c>
@@ -14581,7 +14587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A293" s="7" t="s">
         <v>965</v>
       </c>
@@ -14611,7 +14617,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>345</v>
       </c>
@@ -14643,7 +14649,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
         <v>349</v>
       </c>
@@ -14675,7 +14681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>351</v>
       </c>
@@ -14707,7 +14713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
         <v>353</v>
       </c>
@@ -14739,7 +14745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>355</v>
       </c>
@@ -14771,7 +14777,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
         <v>357</v>
       </c>
@@ -14803,7 +14809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A300" s="7" t="s">
         <v>966</v>
       </c>
@@ -14837,7 +14843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A301" s="7" t="s">
         <v>967</v>
       </c>
@@ -14871,7 +14877,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>359</v>
       </c>
@@ -14901,7 +14907,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
         <v>362</v>
       </c>
@@ -14933,7 +14939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A304" s="8" t="s">
         <v>968</v>
       </c>
@@ -14963,7 +14969,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A305" s="8" t="s">
         <v>969</v>
       </c>
@@ -14993,7 +14999,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A306" s="8" t="s">
         <v>970</v>
       </c>
@@ -15023,7 +15029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
         <v>366</v>
       </c>
@@ -15055,7 +15061,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>368</v>
       </c>
@@ -15087,7 +15093,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
         <v>371</v>
       </c>
@@ -15119,7 +15125,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>375</v>
       </c>
@@ -15151,7 +15157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A311" s="3" t="s">
         <v>377</v>
       </c>
@@ -15181,7 +15187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>381</v>
       </c>
@@ -15213,7 +15219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
         <v>384</v>
       </c>
@@ -15245,7 +15251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A314" s="7" t="s">
         <v>971</v>
       </c>
@@ -15275,7 +15281,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A315" s="7" t="s">
         <v>972</v>
       </c>
@@ -15305,7 +15311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>386</v>
       </c>
@@ -15337,7 +15343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
         <v>388</v>
       </c>
@@ -15369,7 +15375,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>391</v>
       </c>
@@ -15401,7 +15407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
         <v>393</v>
       </c>
@@ -15433,7 +15439,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A320" s="7" t="s">
         <v>973</v>
       </c>
@@ -15463,7 +15469,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
         <v>395</v>
       </c>
@@ -15493,7 +15499,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>397</v>
       </c>
@@ -15525,7 +15531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
         <v>400</v>
       </c>
@@ -15557,7 +15563,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>403</v>
       </c>
@@ -15589,7 +15595,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
         <v>406</v>
       </c>
@@ -15619,7 +15625,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>408</v>
       </c>
@@ -15651,7 +15657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
         <v>412</v>
       </c>
@@ -15683,7 +15689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>415</v>
       </c>
@@ -15715,7 +15721,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
         <v>418</v>
       </c>
@@ -15747,7 +15753,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>422</v>
       </c>
@@ -15781,7 +15787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A331" s="3" t="s">
         <v>424</v>
       </c>
@@ -15815,7 +15821,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A332" s="7" t="s">
         <v>974</v>
       </c>
@@ -15849,7 +15855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
         <v>426</v>
       </c>
@@ -15881,7 +15887,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>429</v>
       </c>
@@ -15911,7 +15917,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
         <v>433</v>
       </c>
@@ -15943,7 +15949,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A336" s="9" t="s">
         <v>975</v>
       </c>
@@ -15973,7 +15979,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
         <v>720</v>
       </c>
@@ -16003,7 +16009,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
         <v>436</v>
       </c>
@@ -16035,7 +16041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>439</v>
       </c>
@@ -16068,11 +16074,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A339">
+    <cfRule type="duplicateValues" dxfId="3" priority="237"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A212 A209 A2:A207">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A339">
-    <cfRule type="duplicateValues" dxfId="2" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="H5" r:id="rId1" xr:uid="{55B3F0D6-E304-4B56-AE2E-288DD1EC76C8}"/>
@@ -16125,23 +16131,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B937977A-AC24-4541-8BF8-4F4772B3F057}">
   <dimension ref="A1:T339"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="3" max="3" width="4.6328125" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" customWidth="1"/>
+    <col min="5" max="6" width="6.36328125" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10.77734375" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" customWidth="1"/>
-    <col min="13" max="13" width="5.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" customWidth="1"/>
+    <col min="11" max="11" width="12.08984375" customWidth="1"/>
+    <col min="12" max="12" width="9.54296875" customWidth="1"/>
+    <col min="13" max="13" width="5.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16185,7 +16191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>780</v>
       </c>
@@ -16219,7 +16225,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -16249,8 +16255,8 @@
         <v>716</v>
       </c>
       <c r="K3" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ref="K3:K8" ca="1" si="0">NOW()</f>
+        <v>46255.970091319447</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>687</v>
@@ -16262,7 +16268,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -16292,8 +16298,8 @@
         <v>716</v>
       </c>
       <c r="K4" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>687</v>
@@ -16305,7 +16311,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>447</v>
       </c>
@@ -16335,8 +16341,8 @@
         <v>18</v>
       </c>
       <c r="K5" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>687</v>
@@ -16345,7 +16351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -16375,8 +16381,8 @@
         <v>716</v>
       </c>
       <c r="K6" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>687</v>
@@ -16385,7 +16391,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -16415,8 +16421,8 @@
         <v>716</v>
       </c>
       <c r="K7" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>687</v>
@@ -16425,7 +16431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>870</v>
       </c>
@@ -16453,8 +16459,8 @@
         <v>716</v>
       </c>
       <c r="K8" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>687</v>
@@ -16463,7 +16469,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>781</v>
       </c>
@@ -16494,7 +16500,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>38</v>
       </c>
@@ -16523,7 +16529,7 @@
       </c>
       <c r="K10" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>687</v>
@@ -16532,7 +16538,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>43</v>
       </c>
@@ -16563,7 +16569,7 @@
       </c>
       <c r="K11" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>687</v>
@@ -16572,7 +16578,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>48</v>
       </c>
@@ -16603,7 +16609,7 @@
       </c>
       <c r="K12" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>687</v>
@@ -16612,7 +16618,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>50</v>
       </c>
@@ -16643,7 +16649,7 @@
       </c>
       <c r="K13" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>687</v>
@@ -16652,7 +16658,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>721</v>
       </c>
@@ -16685,7 +16691,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
@@ -16716,7 +16722,7 @@
       </c>
       <c r="K15" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>687</v>
@@ -16725,7 +16731,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>56</v>
       </c>
@@ -16756,7 +16762,7 @@
       </c>
       <c r="K16" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>687</v>
@@ -16765,7 +16771,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>722</v>
       </c>
@@ -16798,7 +16804,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>61</v>
       </c>
@@ -16829,7 +16835,7 @@
       </c>
       <c r="K18" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>687</v>
@@ -16838,7 +16844,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
@@ -16869,7 +16875,7 @@
       </c>
       <c r="K19" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>687</v>
@@ -16878,7 +16884,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>68</v>
       </c>
@@ -16917,7 +16923,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>70</v>
       </c>
@@ -16956,7 +16962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>72</v>
       </c>
@@ -16995,7 +17001,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>723</v>
       </c>
@@ -17026,7 +17032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>871</v>
       </c>
@@ -17057,7 +17063,7 @@
       </c>
       <c r="K24" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>687</v>
@@ -17066,7 +17072,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>74</v>
       </c>
@@ -17097,7 +17103,7 @@
       </c>
       <c r="K25" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>687</v>
@@ -17106,7 +17112,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>724</v>
       </c>
@@ -17139,7 +17145,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>872</v>
       </c>
@@ -17170,7 +17176,7 @@
       </c>
       <c r="K27" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>687</v>
@@ -17179,7 +17185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>77</v>
       </c>
@@ -17208,7 +17214,7 @@
       </c>
       <c r="K28" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>687</v>
@@ -17217,7 +17223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>82</v>
       </c>
@@ -17248,7 +17254,7 @@
       </c>
       <c r="K29" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>687</v>
@@ -17257,7 +17263,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>84</v>
       </c>
@@ -17288,7 +17294,7 @@
       </c>
       <c r="K30" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>687</v>
@@ -17297,7 +17303,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>725</v>
       </c>
@@ -17330,7 +17336,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>726</v>
       </c>
@@ -17363,7 +17369,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>86</v>
       </c>
@@ -17394,7 +17400,7 @@
       </c>
       <c r="K33" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>687</v>
@@ -17403,7 +17409,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>873</v>
       </c>
@@ -17434,7 +17440,7 @@
       </c>
       <c r="K34" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>687</v>
@@ -17443,7 +17449,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>88</v>
       </c>
@@ -17474,7 +17480,7 @@
       </c>
       <c r="K35" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>687</v>
@@ -17483,7 +17489,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>874</v>
       </c>
@@ -17524,7 +17530,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>93</v>
       </c>
@@ -17555,7 +17561,7 @@
       </c>
       <c r="K37" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>687</v>
@@ -17564,7 +17570,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>1161</v>
       </c>
@@ -17597,7 +17603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>875</v>
       </c>
@@ -17630,7 +17636,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>876</v>
       </c>
@@ -17663,7 +17669,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>803</v>
       </c>
@@ -17696,7 +17702,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>804</v>
       </c>
@@ -17729,7 +17735,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>805</v>
       </c>
@@ -17762,7 +17768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>691</v>
       </c>
@@ -17793,7 +17799,7 @@
       </c>
       <c r="K44" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>687</v>
@@ -17802,7 +17808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>806</v>
       </c>
@@ -17835,7 +17841,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>99</v>
       </c>
@@ -17864,7 +17870,7 @@
       </c>
       <c r="K46" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>687</v>
@@ -17873,7 +17879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>877</v>
       </c>
@@ -17906,7 +17912,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>878</v>
       </c>
@@ -17937,7 +17943,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>101</v>
       </c>
@@ -17968,7 +17974,7 @@
       </c>
       <c r="K49" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>687</v>
@@ -17977,7 +17983,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>807</v>
       </c>
@@ -18010,7 +18016,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>727</v>
       </c>
@@ -18045,7 +18051,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>104</v>
       </c>
@@ -18076,7 +18082,7 @@
       </c>
       <c r="K52" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>687</v>
@@ -18085,7 +18091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>808</v>
       </c>
@@ -18116,7 +18122,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>108</v>
       </c>
@@ -18147,7 +18153,7 @@
       </c>
       <c r="K54" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>687</v>
@@ -18156,7 +18162,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>110</v>
       </c>
@@ -18187,7 +18193,7 @@
       </c>
       <c r="K55" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>687</v>
@@ -18196,7 +18202,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>809</v>
       </c>
@@ -18229,7 +18235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>810</v>
       </c>
@@ -18266,7 +18272,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>112</v>
       </c>
@@ -18297,7 +18303,7 @@
       </c>
       <c r="K58" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>687</v>
@@ -18306,7 +18312,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>879</v>
       </c>
@@ -18347,7 +18353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>115</v>
       </c>
@@ -18378,7 +18384,7 @@
       </c>
       <c r="K60" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>687</v>
@@ -18387,7 +18393,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>880</v>
       </c>
@@ -18424,7 +18430,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>811</v>
       </c>
@@ -18455,7 +18461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>117</v>
       </c>
@@ -18486,7 +18492,7 @@
       </c>
       <c r="K63" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>687</v>
@@ -18495,7 +18501,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
         <v>812</v>
       </c>
@@ -18528,7 +18534,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>881</v>
       </c>
@@ -18565,7 +18571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>882</v>
       </c>
@@ -18606,7 +18612,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>120</v>
       </c>
@@ -18637,7 +18643,7 @@
       </c>
       <c r="K67" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>687</v>
@@ -18646,7 +18652,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>813</v>
       </c>
@@ -18679,7 +18685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>124</v>
       </c>
@@ -18710,7 +18716,7 @@
       </c>
       <c r="K69" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>687</v>
@@ -18719,7 +18725,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>883</v>
       </c>
@@ -18750,7 +18756,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>719</v>
       </c>
@@ -18781,7 +18787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>127</v>
       </c>
@@ -18810,7 +18816,7 @@
       </c>
       <c r="K72" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>687</v>
@@ -18819,7 +18825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>129</v>
       </c>
@@ -18850,7 +18856,7 @@
       </c>
       <c r="K73" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>687</v>
@@ -18859,7 +18865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>884</v>
       </c>
@@ -18890,7 +18896,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>885</v>
       </c>
@@ -18921,7 +18927,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
         <v>814</v>
       </c>
@@ -18952,7 +18958,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>815</v>
       </c>
@@ -18983,7 +18989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>131</v>
       </c>
@@ -19014,7 +19020,7 @@
       </c>
       <c r="K78" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>687</v>
@@ -19023,7 +19029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>886</v>
       </c>
@@ -19054,7 +19060,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>134</v>
       </c>
@@ -19085,7 +19091,7 @@
       </c>
       <c r="K80" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>687</v>
@@ -19094,7 +19100,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>816</v>
       </c>
@@ -19125,7 +19131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>887</v>
       </c>
@@ -19156,7 +19162,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>817</v>
       </c>
@@ -19187,7 +19193,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>888</v>
       </c>
@@ -19218,7 +19224,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>889</v>
       </c>
@@ -19259,7 +19265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>890</v>
       </c>
@@ -19296,7 +19302,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>137</v>
       </c>
@@ -19327,7 +19333,7 @@
       </c>
       <c r="K87" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>687</v>
@@ -19336,7 +19342,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>891</v>
       </c>
@@ -19367,7 +19373,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>892</v>
       </c>
@@ -19398,7 +19404,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>893</v>
       </c>
@@ -19435,7 +19441,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>894</v>
       </c>
@@ -19472,7 +19478,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>895</v>
       </c>
@@ -19503,7 +19509,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>896</v>
       </c>
@@ -19534,7 +19540,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>897</v>
       </c>
@@ -19565,7 +19571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>898</v>
       </c>
@@ -19596,7 +19602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>899</v>
       </c>
@@ -19627,7 +19633,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>900</v>
       </c>
@@ -19658,7 +19664,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>901</v>
       </c>
@@ -19689,7 +19695,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
         <v>818</v>
       </c>
@@ -19720,7 +19726,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>902</v>
       </c>
@@ -19751,7 +19757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
         <v>819</v>
       </c>
@@ -19782,7 +19788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>903</v>
       </c>
@@ -19813,7 +19819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>904</v>
       </c>
@@ -19844,7 +19850,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>905</v>
       </c>
@@ -19885,7 +19891,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>906</v>
       </c>
@@ -19916,7 +19922,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="8" t="s">
         <v>820</v>
       </c>
@@ -19947,7 +19953,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>139</v>
       </c>
@@ -19978,7 +19984,7 @@
       </c>
       <c r="K107" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>687</v>
@@ -19987,7 +19993,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
         <v>821</v>
       </c>
@@ -20021,7 +20027,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="8" t="s">
         <v>822</v>
       </c>
@@ -20055,7 +20061,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="8" t="s">
         <v>823</v>
       </c>
@@ -20089,7 +20095,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>907</v>
       </c>
@@ -20129,7 +20135,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="8" t="s">
         <v>824</v>
       </c>
@@ -20163,7 +20169,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>141</v>
       </c>
@@ -20194,7 +20200,7 @@
       </c>
       <c r="K113" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L113" s="5" t="s">
         <v>687</v>
@@ -20206,7 +20212,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>908</v>
       </c>
@@ -20240,7 +20246,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>144</v>
       </c>
@@ -20271,7 +20277,7 @@
       </c>
       <c r="K115" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>687</v>
@@ -20283,7 +20289,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>147</v>
       </c>
@@ -20314,7 +20320,7 @@
       </c>
       <c r="K116" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>687</v>
@@ -20326,7 +20332,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>909</v>
       </c>
@@ -20360,7 +20366,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>910</v>
       </c>
@@ -20394,7 +20400,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>150</v>
       </c>
@@ -20425,7 +20431,7 @@
       </c>
       <c r="K119" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L119" s="5" t="s">
         <v>687</v>
@@ -20437,7 +20443,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>825</v>
       </c>
@@ -20475,7 +20481,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>911</v>
       </c>
@@ -20509,7 +20515,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>152</v>
       </c>
@@ -20540,7 +20546,7 @@
       </c>
       <c r="K122" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L122" s="5" t="s">
         <v>687</v>
@@ -20552,7 +20558,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>154</v>
       </c>
@@ -20583,7 +20589,7 @@
       </c>
       <c r="K123" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L123" s="5" t="s">
         <v>687</v>
@@ -20595,7 +20601,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>912</v>
       </c>
@@ -20629,7 +20635,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>913</v>
       </c>
@@ -20673,7 +20679,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>914</v>
       </c>
@@ -20707,7 +20713,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>156</v>
       </c>
@@ -20738,7 +20744,7 @@
       </c>
       <c r="K127" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L127" s="5" t="s">
         <v>687</v>
@@ -20750,7 +20756,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>915</v>
       </c>
@@ -20784,7 +20790,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>916</v>
       </c>
@@ -20813,7 +20819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="8" t="s">
         <v>826</v>
       </c>
@@ -20844,7 +20850,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>917</v>
       </c>
@@ -20881,7 +20887,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>918</v>
       </c>
@@ -20912,7 +20918,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>919</v>
       </c>
@@ -20949,7 +20955,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
         <v>920</v>
       </c>
@@ -20990,7 +20996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>159</v>
       </c>
@@ -21021,7 +21027,7 @@
       </c>
       <c r="K135" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L135" s="5" t="s">
         <v>687</v>
@@ -21030,7 +21036,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>162</v>
       </c>
@@ -21061,7 +21067,7 @@
       </c>
       <c r="K136" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L136" s="5" t="s">
         <v>687</v>
@@ -21070,7 +21076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>921</v>
       </c>
@@ -21111,7 +21117,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>922</v>
       </c>
@@ -21142,7 +21148,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>827</v>
       </c>
@@ -21173,7 +21179,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>923</v>
       </c>
@@ -21204,7 +21210,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>924</v>
       </c>
@@ -21235,7 +21241,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>925</v>
       </c>
@@ -21266,7 +21272,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>926</v>
       </c>
@@ -21297,7 +21303,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>927</v>
       </c>
@@ -21328,7 +21334,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>697</v>
       </c>
@@ -21359,7 +21365,7 @@
       </c>
       <c r="K145" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L145" s="5" t="s">
         <v>687</v>
@@ -21368,7 +21374,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>167</v>
       </c>
@@ -21399,7 +21405,7 @@
       </c>
       <c r="K146" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L146" s="5" t="s">
         <v>687</v>
@@ -21408,7 +21414,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>928</v>
       </c>
@@ -21445,7 +21451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>929</v>
       </c>
@@ -21476,7 +21482,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>828</v>
       </c>
@@ -21507,7 +21513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>930</v>
       </c>
@@ -21548,7 +21554,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="8" t="s">
         <v>829</v>
       </c>
@@ -21577,7 +21583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>931</v>
       </c>
@@ -21614,7 +21620,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>932</v>
       </c>
@@ -21645,7 +21651,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>933</v>
       </c>
@@ -21676,7 +21682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="8" t="s">
         <v>830</v>
       </c>
@@ -21707,7 +21713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>934</v>
       </c>
@@ -21738,7 +21744,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="8" t="s">
         <v>831</v>
       </c>
@@ -21769,7 +21775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>935</v>
       </c>
@@ -21806,7 +21812,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="8" t="s">
         <v>832</v>
       </c>
@@ -21837,7 +21843,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
         <v>172</v>
       </c>
@@ -21868,7 +21874,7 @@
       </c>
       <c r="K160" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L160" s="5" t="s">
         <v>687</v>
@@ -21877,7 +21883,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="8" t="s">
         <v>936</v>
       </c>
@@ -21908,7 +21914,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>833</v>
       </c>
@@ -21949,7 +21955,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>175</v>
       </c>
@@ -21980,7 +21986,7 @@
       </c>
       <c r="K163" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L163" s="5" t="s">
         <v>687</v>
@@ -21989,7 +21995,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>834</v>
       </c>
@@ -22030,7 +22036,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
         <v>937</v>
       </c>
@@ -22067,7 +22073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
         <v>835</v>
       </c>
@@ -22098,7 +22104,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>177</v>
       </c>
@@ -22129,7 +22135,7 @@
       </c>
       <c r="K167" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L167" s="5" t="s">
         <v>687</v>
@@ -22138,7 +22144,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
         <v>836</v>
       </c>
@@ -22169,7 +22175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="9" t="s">
         <v>837</v>
       </c>
@@ -22200,7 +22206,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="8" t="s">
         <v>838</v>
       </c>
@@ -22231,7 +22237,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>180</v>
       </c>
@@ -22262,7 +22268,7 @@
       </c>
       <c r="K171" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L171" s="5" t="s">
         <v>687</v>
@@ -22271,7 +22277,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="8" t="s">
         <v>839</v>
       </c>
@@ -22302,7 +22308,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="8" t="s">
         <v>840</v>
       </c>
@@ -22333,7 +22339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
         <v>182</v>
       </c>
@@ -22364,7 +22370,7 @@
       </c>
       <c r="K174" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L174" s="5" t="s">
         <v>687</v>
@@ -22373,7 +22379,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>184</v>
       </c>
@@ -22402,7 +22408,7 @@
       </c>
       <c r="K175" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L175" s="5" t="s">
         <v>687</v>
@@ -22411,7 +22417,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
         <v>188</v>
       </c>
@@ -22442,7 +22448,7 @@
       </c>
       <c r="K176" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L176" s="5" t="s">
         <v>687</v>
@@ -22451,7 +22457,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
         <v>938</v>
       </c>
@@ -22482,7 +22488,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="8" t="s">
         <v>841</v>
       </c>
@@ -22513,7 +22519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="9" t="s">
         <v>779</v>
       </c>
@@ -22546,7 +22552,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
         <v>190</v>
       </c>
@@ -22577,7 +22583,7 @@
       </c>
       <c r="K180" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L180" s="5" t="s">
         <v>687</v>
@@ -22586,7 +22592,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>939</v>
       </c>
@@ -22627,7 +22633,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
         <v>842</v>
       </c>
@@ -22668,7 +22674,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>193</v>
       </c>
@@ -22699,7 +22705,7 @@
       </c>
       <c r="K183" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L183" s="5" t="s">
         <v>687</v>
@@ -22708,7 +22714,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
         <v>195</v>
       </c>
@@ -22739,7 +22745,7 @@
       </c>
       <c r="K184" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L184" s="5" t="s">
         <v>687</v>
@@ -22748,7 +22754,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
         <v>940</v>
       </c>
@@ -22785,7 +22791,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
         <v>843</v>
       </c>
@@ -22826,7 +22832,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="9" t="s">
         <v>941</v>
       </c>
@@ -22857,7 +22863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="8" t="s">
         <v>844</v>
       </c>
@@ -22888,7 +22894,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>198</v>
       </c>
@@ -22919,7 +22925,7 @@
       </c>
       <c r="K189" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L189" s="5" t="s">
         <v>687</v>
@@ -22928,7 +22934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="8" t="s">
         <v>845</v>
       </c>
@@ -22959,7 +22965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>202</v>
       </c>
@@ -22990,7 +22996,7 @@
       </c>
       <c r="K191" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L191" s="5" t="s">
         <v>687</v>
@@ -22999,7 +23005,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="8" t="s">
         <v>846</v>
       </c>
@@ -23028,7 +23034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>204</v>
       </c>
@@ -23059,7 +23065,7 @@
       </c>
       <c r="K193" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L193" s="5" t="s">
         <v>687</v>
@@ -23068,7 +23074,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="8" t="s">
         <v>847</v>
       </c>
@@ -23099,7 +23105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>206</v>
       </c>
@@ -23130,7 +23136,7 @@
       </c>
       <c r="K195" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L195" s="5" t="s">
         <v>687</v>
@@ -23139,7 +23145,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
         <v>208</v>
       </c>
@@ -23170,7 +23176,7 @@
       </c>
       <c r="K196" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L196" s="5" t="s">
         <v>687</v>
@@ -23179,7 +23185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>212</v>
       </c>
@@ -23210,7 +23216,7 @@
       </c>
       <c r="K197" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L197" s="5" t="s">
         <v>687</v>
@@ -23219,7 +23225,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="8" t="s">
         <v>848</v>
       </c>
@@ -23250,7 +23256,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>214</v>
       </c>
@@ -23281,7 +23287,7 @@
       </c>
       <c r="K199" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L199" s="5" t="s">
         <v>687</v>
@@ -23290,7 +23296,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>217</v>
       </c>
@@ -23319,7 +23325,7 @@
       </c>
       <c r="K200" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L200" s="5" t="s">
         <v>687</v>
@@ -23328,7 +23334,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
         <v>219</v>
       </c>
@@ -23359,7 +23365,7 @@
       </c>
       <c r="K201" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L201" s="5" t="s">
         <v>687</v>
@@ -23368,7 +23374,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="8" t="s">
         <v>849</v>
       </c>
@@ -23401,7 +23407,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
         <v>221</v>
       </c>
@@ -23432,7 +23438,7 @@
       </c>
       <c r="K203" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L203" s="5" t="s">
         <v>687</v>
@@ -23441,7 +23447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>224</v>
       </c>
@@ -23472,7 +23478,7 @@
       </c>
       <c r="K204" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L204" s="5" t="s">
         <v>687</v>
@@ -23481,7 +23487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="8" t="s">
         <v>850</v>
       </c>
@@ -23512,7 +23518,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>227</v>
       </c>
@@ -23543,7 +23549,7 @@
       </c>
       <c r="K206" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L206" s="5" t="s">
         <v>687</v>
@@ -23552,7 +23558,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
         <v>942</v>
       </c>
@@ -23581,7 +23587,7 @@
       </c>
       <c r="K207" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L207" s="5" t="s">
         <v>687</v>
@@ -23590,7 +23596,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="8" t="s">
         <v>851</v>
       </c>
@@ -23621,7 +23627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="8" t="s">
         <v>852</v>
       </c>
@@ -23652,7 +23658,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="8" t="s">
         <v>853</v>
       </c>
@@ -23681,7 +23687,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
         <v>231</v>
       </c>
@@ -23712,7 +23718,7 @@
       </c>
       <c r="K211" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L211" s="5" t="s">
         <v>687</v>
@@ -23721,7 +23727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>442</v>
       </c>
@@ -23762,7 +23768,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="213" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
         <v>234</v>
       </c>
@@ -23793,7 +23799,7 @@
       </c>
       <c r="K213" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L213" s="5" t="s">
         <v>687</v>
@@ -23802,7 +23808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="8" t="s">
         <v>943</v>
       </c>
@@ -23833,7 +23839,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
         <v>237</v>
       </c>
@@ -23862,7 +23868,7 @@
       </c>
       <c r="K215" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L215" s="5" t="s">
         <v>687</v>
@@ -23871,7 +23877,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="8" t="s">
         <v>854</v>
       </c>
@@ -23902,7 +23908,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="217" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
         <v>784</v>
       </c>
@@ -23935,7 +23941,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="218" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>240</v>
       </c>
@@ -23966,7 +23972,7 @@
       </c>
       <c r="K218" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L218" s="5" t="s">
         <v>687</v>
@@ -23975,7 +23981,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
         <v>944</v>
       </c>
@@ -24012,7 +24018,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="220" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" s="8" t="s">
         <v>855</v>
       </c>
@@ -24043,7 +24049,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
         <v>243</v>
       </c>
@@ -24074,7 +24080,7 @@
       </c>
       <c r="K221" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L221" s="5" t="s">
         <v>687</v>
@@ -24083,7 +24089,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="8" t="s">
         <v>856</v>
       </c>
@@ -24112,7 +24118,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="8" t="s">
         <v>857</v>
       </c>
@@ -24143,7 +24149,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="224" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>245</v>
       </c>
@@ -24172,7 +24178,7 @@
       </c>
       <c r="K224" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L224" s="5" t="s">
         <v>687</v>
@@ -24181,7 +24187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="225" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
         <v>246</v>
       </c>
@@ -24212,7 +24218,7 @@
       </c>
       <c r="K225" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L225" s="5" t="s">
         <v>687</v>
@@ -24221,7 +24227,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="226" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>249</v>
       </c>
@@ -24252,7 +24258,7 @@
       </c>
       <c r="K226" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L226" s="5" t="s">
         <v>687</v>
@@ -24261,7 +24267,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
         <v>945</v>
       </c>
@@ -24302,7 +24308,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>252</v>
       </c>
@@ -24331,7 +24337,7 @@
       </c>
       <c r="K228" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L228" s="5" t="s">
         <v>687</v>
@@ -24340,7 +24346,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
         <v>256</v>
       </c>
@@ -24371,7 +24377,7 @@
       </c>
       <c r="K229" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L229" s="5" t="s">
         <v>687</v>
@@ -24380,7 +24386,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>698</v>
       </c>
@@ -24411,7 +24417,7 @@
       </c>
       <c r="K230" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L230" s="5" t="s">
         <v>687</v>
@@ -24420,7 +24426,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="231" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="7" t="s">
         <v>858</v>
       </c>
@@ -24461,7 +24467,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>260</v>
       </c>
@@ -24492,7 +24498,7 @@
       </c>
       <c r="K232" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L232" s="5" t="s">
         <v>687</v>
@@ -24501,7 +24507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="233" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
         <v>263</v>
       </c>
@@ -24532,7 +24538,7 @@
       </c>
       <c r="K233" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L233" s="5" t="s">
         <v>687</v>
@@ -24541,7 +24547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>265</v>
       </c>
@@ -24572,7 +24578,7 @@
       </c>
       <c r="K234" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L234" s="5" t="s">
         <v>687</v>
@@ -24581,7 +24587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="8" t="s">
         <v>859</v>
       </c>
@@ -24612,7 +24618,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="236" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" s="7" t="s">
         <v>946</v>
       </c>
@@ -24649,7 +24655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
         <v>267</v>
       </c>
@@ -24680,7 +24686,7 @@
       </c>
       <c r="K237" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L237" s="5" t="s">
         <v>687</v>
@@ -24689,7 +24695,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="7" t="s">
         <v>947</v>
       </c>
@@ -24726,7 +24732,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="239" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="7" t="s">
         <v>948</v>
       </c>
@@ -24767,7 +24773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="240" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>717</v>
       </c>
@@ -24798,7 +24804,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
         <v>949</v>
       </c>
@@ -24827,7 +24833,7 @@
       </c>
       <c r="K241" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L241" s="5" t="s">
         <v>687</v>
@@ -24836,7 +24842,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="7" t="s">
         <v>950</v>
       </c>
@@ -24873,7 +24879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" s="3" t="s">
         <v>951</v>
       </c>
@@ -24902,7 +24908,7 @@
       </c>
       <c r="K243" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L243" s="5" t="s">
         <v>687</v>
@@ -24911,7 +24917,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" s="9" t="s">
         <v>952</v>
       </c>
@@ -24942,7 +24948,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="245" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
         <v>272</v>
       </c>
@@ -24973,7 +24979,7 @@
       </c>
       <c r="K245" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L245" s="5" t="s">
         <v>687</v>
@@ -24982,7 +24988,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="246" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>274</v>
       </c>
@@ -25013,7 +25019,7 @@
       </c>
       <c r="K246" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L246" s="5" t="s">
         <v>687</v>
@@ -25022,7 +25028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="247" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
         <v>278</v>
       </c>
@@ -25053,7 +25059,7 @@
       </c>
       <c r="K247" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L247" s="5" t="s">
         <v>687</v>
@@ -25062,7 +25068,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="248" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>283</v>
       </c>
@@ -25093,7 +25099,7 @@
       </c>
       <c r="K248" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L248" s="5" t="s">
         <v>687</v>
@@ -25102,7 +25108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="249" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A249" s="7" t="s">
         <v>953</v>
       </c>
@@ -25139,7 +25145,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="250" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A250" s="8" t="s">
         <v>860</v>
       </c>
@@ -25170,7 +25176,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
         <v>286</v>
       </c>
@@ -25201,7 +25207,7 @@
       </c>
       <c r="K251" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L251" s="5" t="s">
         <v>687</v>
@@ -25210,7 +25216,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="252" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>289</v>
       </c>
@@ -25239,7 +25245,7 @@
       </c>
       <c r="K252" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L252" s="5" t="s">
         <v>687</v>
@@ -25248,7 +25254,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="253" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="8" t="s">
         <v>861</v>
       </c>
@@ -25279,7 +25285,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" s="7" t="s">
         <v>954</v>
       </c>
@@ -25312,7 +25318,7 @@
       </c>
       <c r="K254" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L254" s="5" t="s">
         <v>687</v>
@@ -25321,7 +25327,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" s="8" t="s">
         <v>862</v>
       </c>
@@ -25352,7 +25358,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="256" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" s="7" t="s">
         <v>863</v>
       </c>
@@ -25389,7 +25395,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="257" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
         <v>294</v>
       </c>
@@ -25418,7 +25424,7 @@
       </c>
       <c r="K257" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L257" s="5" t="s">
         <v>687</v>
@@ -25427,7 +25433,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="258" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>297</v>
       </c>
@@ -25458,7 +25464,7 @@
       </c>
       <c r="K258" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L258" s="5" t="s">
         <v>687</v>
@@ -25467,7 +25473,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="259" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
         <v>300</v>
       </c>
@@ -25498,7 +25504,7 @@
       </c>
       <c r="K259" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L259" s="5" t="s">
         <v>687</v>
@@ -25507,7 +25513,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="260" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="8" t="s">
         <v>864</v>
       </c>
@@ -25536,7 +25542,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
         <v>302</v>
       </c>
@@ -25567,7 +25573,7 @@
       </c>
       <c r="K261" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L261" s="5" t="s">
         <v>687</v>
@@ -25576,7 +25582,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>304</v>
       </c>
@@ -25607,7 +25613,7 @@
       </c>
       <c r="K262" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L262" s="5" t="s">
         <v>687</v>
@@ -25616,7 +25622,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="263" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" s="7" t="s">
         <v>955</v>
       </c>
@@ -25653,7 +25659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="264" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A264" s="7" t="s">
         <v>865</v>
       </c>
@@ -25690,7 +25696,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="265" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A265" s="8" t="s">
         <v>866</v>
       </c>
@@ -25721,7 +25727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="266" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
         <v>956</v>
       </c>
@@ -25750,7 +25756,7 @@
       </c>
       <c r="K266" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L266" s="5" t="s">
         <v>687</v>
@@ -25759,7 +25765,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="267" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
         <v>309</v>
       </c>
@@ -25790,7 +25796,7 @@
       </c>
       <c r="K267" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L267" s="5" t="s">
         <v>687</v>
@@ -25799,7 +25805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="268" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A268" s="8" t="s">
         <v>867</v>
       </c>
@@ -25830,7 +25836,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="269" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
         <v>311</v>
       </c>
@@ -25861,7 +25867,7 @@
       </c>
       <c r="K269" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L269" s="5" t="s">
         <v>687</v>
@@ -25870,7 +25876,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="270" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A270" s="8" t="s">
         <v>868</v>
       </c>
@@ -25901,7 +25907,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A271" s="8" t="s">
         <v>785</v>
       </c>
@@ -25930,7 +25936,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A272" s="7" t="s">
         <v>957</v>
       </c>
@@ -25967,7 +25973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A273" s="7" t="s">
         <v>958</v>
       </c>
@@ -26004,7 +26010,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A274" s="8" t="s">
         <v>869</v>
       </c>
@@ -26035,7 +26041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
         <v>314</v>
       </c>
@@ -26066,7 +26072,7 @@
       </c>
       <c r="K275" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L275" s="5" t="s">
         <v>687</v>
@@ -26075,7 +26081,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="276" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A276" s="7" t="s">
         <v>959</v>
       </c>
@@ -26112,7 +26118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A277" s="7" t="s">
         <v>960</v>
       </c>
@@ -26149,7 +26155,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>316</v>
       </c>
@@ -26180,7 +26186,7 @@
       </c>
       <c r="K278" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L278" s="5" t="s">
         <v>687</v>
@@ -26189,7 +26195,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A279" s="7" t="s">
         <v>961</v>
       </c>
@@ -26230,7 +26236,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>318</v>
       </c>
@@ -26261,7 +26267,7 @@
       </c>
       <c r="K280" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L280" s="5" t="s">
         <v>687</v>
@@ -26270,7 +26276,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
         <v>320</v>
       </c>
@@ -26301,7 +26307,7 @@
       </c>
       <c r="K281" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L281" s="5" t="s">
         <v>687</v>
@@ -26310,7 +26316,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
         <v>323</v>
       </c>
@@ -26341,7 +26347,7 @@
       </c>
       <c r="K282" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L282" s="5" t="s">
         <v>687</v>
@@ -26350,7 +26356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
         <v>325</v>
       </c>
@@ -26381,7 +26387,7 @@
       </c>
       <c r="K283" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L283" s="5" t="s">
         <v>687</v>
@@ -26390,7 +26396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A284" s="7" t="s">
         <v>963</v>
       </c>
@@ -26431,7 +26437,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
         <v>962</v>
       </c>
@@ -26460,7 +26466,7 @@
       </c>
       <c r="K285" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L285" s="5" t="s">
         <v>687</v>
@@ -26469,7 +26475,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
         <v>329</v>
       </c>
@@ -26500,7 +26506,7 @@
       </c>
       <c r="K286" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L286" s="5" t="s">
         <v>687</v>
@@ -26509,7 +26515,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
         <v>333</v>
       </c>
@@ -26540,7 +26546,7 @@
       </c>
       <c r="K287" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L287" s="5" t="s">
         <v>687</v>
@@ -26549,7 +26555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A288" s="7" t="s">
         <v>964</v>
       </c>
@@ -26586,7 +26592,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
         <v>335</v>
       </c>
@@ -26617,7 +26623,7 @@
       </c>
       <c r="K289" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L289" s="5" t="s">
         <v>687</v>
@@ -26626,7 +26632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>337</v>
       </c>
@@ -26657,7 +26663,7 @@
       </c>
       <c r="K290" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L290" s="5" t="s">
         <v>687</v>
@@ -26666,7 +26672,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
         <v>340</v>
       </c>
@@ -26697,7 +26703,7 @@
       </c>
       <c r="K291" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L291" s="5" t="s">
         <v>687</v>
@@ -26706,7 +26712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>342</v>
       </c>
@@ -26737,7 +26743,7 @@
       </c>
       <c r="K292" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L292" s="5" t="s">
         <v>687</v>
@@ -26746,7 +26752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A293" s="7" t="s">
         <v>965</v>
       </c>
@@ -26783,7 +26789,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>345</v>
       </c>
@@ -26813,8 +26819,8 @@
         <v>716</v>
       </c>
       <c r="K294" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ref="K294:K299" ca="1" si="1">NOW()</f>
+        <v>46255.970091319447</v>
       </c>
       <c r="L294" s="5" t="s">
         <v>687</v>
@@ -26823,7 +26829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
         <v>349</v>
       </c>
@@ -26853,8 +26859,8 @@
         <v>716</v>
       </c>
       <c r="K295" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L295" s="5" t="s">
         <v>687</v>
@@ -26863,7 +26869,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>351</v>
       </c>
@@ -26893,8 +26899,8 @@
         <v>716</v>
       </c>
       <c r="K296" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L296" s="5" t="s">
         <v>687</v>
@@ -26903,7 +26909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
         <v>353</v>
       </c>
@@ -26933,8 +26939,8 @@
         <v>716</v>
       </c>
       <c r="K297" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L297" s="5" t="s">
         <v>687</v>
@@ -26943,7 +26949,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>355</v>
       </c>
@@ -26973,8 +26979,8 @@
         <v>716</v>
       </c>
       <c r="K298" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L298" s="5" t="s">
         <v>687</v>
@@ -26983,7 +26989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
         <v>357</v>
       </c>
@@ -27013,8 +27019,8 @@
         <v>716</v>
       </c>
       <c r="K299" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L299" s="5" t="s">
         <v>687</v>
@@ -27023,7 +27029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A300" s="7" t="s">
         <v>966</v>
       </c>
@@ -27064,7 +27070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A301" s="7" t="s">
         <v>967</v>
       </c>
@@ -27105,7 +27111,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>359</v>
       </c>
@@ -27134,7 +27140,7 @@
       </c>
       <c r="K302" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L302" s="5" t="s">
         <v>687</v>
@@ -27143,7 +27149,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
         <v>362</v>
       </c>
@@ -27174,7 +27180,7 @@
       </c>
       <c r="K303" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L303" s="5" t="s">
         <v>687</v>
@@ -27183,7 +27189,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A304" s="8" t="s">
         <v>968</v>
       </c>
@@ -27214,7 +27220,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A305" s="8" t="s">
         <v>969</v>
       </c>
@@ -27245,7 +27251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A306" s="8" t="s">
         <v>970</v>
       </c>
@@ -27276,7 +27282,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
         <v>366</v>
       </c>
@@ -27306,8 +27312,8 @@
         <v>716</v>
       </c>
       <c r="K307" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ref="K307:K313" ca="1" si="2">NOW()</f>
+        <v>46255.970091319447</v>
       </c>
       <c r="L307" s="5" t="s">
         <v>687</v>
@@ -27316,7 +27322,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>368</v>
       </c>
@@ -27346,8 +27352,8 @@
         <v>716</v>
       </c>
       <c r="K308" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L308" s="5" t="s">
         <v>687</v>
@@ -27356,7 +27362,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
         <v>371</v>
       </c>
@@ -27386,8 +27392,8 @@
         <v>716</v>
       </c>
       <c r="K309" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L309" s="5" t="s">
         <v>687</v>
@@ -27396,7 +27402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>375</v>
       </c>
@@ -27426,8 +27432,8 @@
         <v>716</v>
       </c>
       <c r="K310" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L310" s="5" t="s">
         <v>687</v>
@@ -27436,7 +27442,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A311" s="3" t="s">
         <v>377</v>
       </c>
@@ -27464,8 +27470,8 @@
         <v>716</v>
       </c>
       <c r="K311" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L311" s="5" t="s">
         <v>687</v>
@@ -27474,7 +27480,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>381</v>
       </c>
@@ -27504,8 +27510,8 @@
         <v>716</v>
       </c>
       <c r="K312" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L312" s="5" t="s">
         <v>687</v>
@@ -27514,7 +27520,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
         <v>384</v>
       </c>
@@ -27544,8 +27550,8 @@
         <v>716</v>
       </c>
       <c r="K313" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L313" s="5" t="s">
         <v>687</v>
@@ -27554,7 +27560,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A314" s="7" t="s">
         <v>971</v>
       </c>
@@ -27591,7 +27597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A315" s="7" t="s">
         <v>972</v>
       </c>
@@ -27628,7 +27634,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>386</v>
       </c>
@@ -27659,7 +27665,7 @@
       </c>
       <c r="K316" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L316" s="5" t="s">
         <v>687</v>
@@ -27668,7 +27674,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
         <v>388</v>
       </c>
@@ -27699,7 +27705,7 @@
       </c>
       <c r="K317" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L317" s="5" t="s">
         <v>687</v>
@@ -27708,7 +27714,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>391</v>
       </c>
@@ -27739,7 +27745,7 @@
       </c>
       <c r="K318" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L318" s="5" t="s">
         <v>687</v>
@@ -27748,7 +27754,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
         <v>393</v>
       </c>
@@ -27779,7 +27785,7 @@
       </c>
       <c r="K319" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L319" s="5" t="s">
         <v>687</v>
@@ -27788,7 +27794,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A320" s="7" t="s">
         <v>973</v>
       </c>
@@ -27825,7 +27831,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
         <v>395</v>
       </c>
@@ -27853,8 +27859,8 @@
         <v>716</v>
       </c>
       <c r="K321" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ref="K321:K331" ca="1" si="3">NOW()</f>
+        <v>46255.970091319447</v>
       </c>
       <c r="L321" s="5" t="s">
         <v>687</v>
@@ -27863,7 +27869,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>397</v>
       </c>
@@ -27893,8 +27899,8 @@
         <v>716</v>
       </c>
       <c r="K322" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L322" s="5" t="s">
         <v>687</v>
@@ -27903,7 +27909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
         <v>400</v>
       </c>
@@ -27933,8 +27939,8 @@
         <v>716</v>
       </c>
       <c r="K323" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L323" s="5" t="s">
         <v>687</v>
@@ -27943,7 +27949,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>403</v>
       </c>
@@ -27973,8 +27979,8 @@
         <v>716</v>
       </c>
       <c r="K324" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L324" s="5" t="s">
         <v>687</v>
@@ -27983,7 +27989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
         <v>406</v>
       </c>
@@ -28011,8 +28017,8 @@
         <v>716</v>
       </c>
       <c r="K325" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L325" s="5" t="s">
         <v>687</v>
@@ -28021,7 +28027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>408</v>
       </c>
@@ -28051,8 +28057,8 @@
         <v>716</v>
       </c>
       <c r="K326" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L326" s="5" t="s">
         <v>687</v>
@@ -28061,7 +28067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
         <v>412</v>
       </c>
@@ -28091,8 +28097,8 @@
         <v>716</v>
       </c>
       <c r="K327" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L327" s="5" t="s">
         <v>687</v>
@@ -28101,7 +28107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>415</v>
       </c>
@@ -28131,8 +28137,8 @@
         <v>716</v>
       </c>
       <c r="K328" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L328" s="5" t="s">
         <v>687</v>
@@ -28141,7 +28147,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
         <v>418</v>
       </c>
@@ -28171,8 +28177,8 @@
         <v>716</v>
       </c>
       <c r="K329" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L329" s="5" t="s">
         <v>687</v>
@@ -28181,7 +28187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>422</v>
       </c>
@@ -28213,8 +28219,8 @@
         <v>716</v>
       </c>
       <c r="K330" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L330" s="5" t="s">
         <v>687</v>
@@ -28223,7 +28229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A331" s="3" t="s">
         <v>424</v>
       </c>
@@ -28255,8 +28261,8 @@
         <v>716</v>
       </c>
       <c r="K331" s="5">
-        <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46255.970091319447</v>
       </c>
       <c r="L331" s="5" t="s">
         <v>687</v>
@@ -28265,7 +28271,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A332" s="7" t="s">
         <v>974</v>
       </c>
@@ -28306,7 +28312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
         <v>426</v>
       </c>
@@ -28337,7 +28343,7 @@
       </c>
       <c r="K333" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L333" s="5" t="s">
         <v>687</v>
@@ -28346,7 +28352,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>429</v>
       </c>
@@ -28375,7 +28381,7 @@
       </c>
       <c r="K334" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L334" s="5" t="s">
         <v>687</v>
@@ -28384,7 +28390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
         <v>433</v>
       </c>
@@ -28415,7 +28421,7 @@
       </c>
       <c r="K335" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L335" s="5" t="s">
         <v>687</v>
@@ -28424,7 +28430,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A336" s="9" t="s">
         <v>975</v>
       </c>
@@ -28455,7 +28461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
         <v>720</v>
       </c>
@@ -28486,7 +28492,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
         <v>436</v>
       </c>
@@ -28517,7 +28523,7 @@
       </c>
       <c r="K338" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L338" s="5" t="s">
         <v>687</v>
@@ -28526,7 +28532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>439</v>
       </c>
@@ -28557,7 +28563,7 @@
       </c>
       <c r="K339" s="5">
         <f ca="1">NOW()</f>
-        <v>46190.112033680554</v>
+        <v>46255.970091319447</v>
       </c>
       <c r="L339" s="5" t="s">
         <v>687</v>
@@ -28567,11 +28573,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A339">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A212 A209 A2:A207">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A339">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J339" xr:uid="{8176762B-72D4-49FF-B4B7-F4FD41147861}">
@@ -28629,7 +28635,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74850CC2-13F5-4E0C-967C-0B64D2C338D2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
